--- a/artfynd/A 56521-2025 artfynd.xlsx
+++ b/artfynd/A 56521-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121343355</v>
+        <v>121343353</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437518</v>
+        <v>437656</v>
       </c>
       <c r="R2" t="n">
-        <v>6856875</v>
+        <v>6856774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>glest bevuxen myr</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,12 +780,7 @@
         <v>121343351</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,6 +871,307 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121343354</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flöskesåsvallen O ca 1,3 km, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>437629</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6856759</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>glest bevuxen myr</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121343355</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flöskesåsvallen O ca 1,3 km, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>437518</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6856875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121343352</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flöskesåsvallen O ca 1,3 km, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>437656</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6856774</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>glest bevuxen myr</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56521-2025 artfynd.xlsx
+++ b/artfynd/A 56521-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343351</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343354</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343355</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,8 +1197,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121343352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>